--- a/data/trans_dic/KIDMED_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/KIDMED_R2-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,26</t>
+          <t>0,0; 2,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 3,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,95</t>
+          <t>0,59; 3,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,63</t>
+          <t>0,18; 2,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,62</t>
+          <t>0,58; 2,42</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,56</t>
+          <t>4,01; 11,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 11,39</t>
+          <t>1,66; 6,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 7,56</t>
+          <t>3,45; 8,31</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 9,08</t>
+          <t>1,51; 8,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 7,88</t>
+          <t>2,95; 9,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 7,3</t>
+          <t>3,08; 7,54</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,81</t>
+          <t>2,1; 4,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,77</t>
+          <t>1,82; 4,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,88</t>
+          <t>2,26; 4,02</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>641</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>756</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1397</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3727</t>
+          <t>0; 3416</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3766</t>
+          <t>0; 3828</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5012</t>
+          <t>0; 4673</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>4940</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>381; 3632</t>
+          <t>1353; 7483</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1514; 8990</t>
+          <t>322; 3659</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2869; 11354</t>
+          <t>2402; 9975</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>11681</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>17436</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2227; 10466</t>
+          <t>6679; 18886</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7398; 20851</t>
+          <t>2578; 10840</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11170; 28059</t>
+          <t>11106; 26723</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>9074</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>9505</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15717</t>
+          <t>15847</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4723; 14941</t>
+          <t>2517; 13781</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2881; 13973</t>
+          <t>4843; 15888</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9496; 24955</t>
+          <t>10180; 24882</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>22371</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41084</t>
+          <t>39620</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11175; 24904</t>
+          <t>14389; 31658</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16282; 35530</t>
+          <t>11233; 25225</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30492; 54260</t>
+          <t>29442; 52502</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/KIDMED_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/KIDMED_R2-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que tienen una baja adherencia a la dieta mediterránea (tasa de respuesta: 96,61%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,78</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,23</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,93</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,59; 3,24</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,18; 2,03</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,58; 2,42</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>4,01; 11,34</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,66; 6,99</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>3,45; 8,31</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>1,51; 8,29</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2,95; 9,69</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3,08; 7,54</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3,04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>2,1; 4,61</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1,82; 4,08</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2,26; 4,02</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.00521865948147316</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.006372977016304249</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.005785544651540363</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>756</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1397</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3416</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3828</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4673</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.02779392396198348</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.03228097801922518</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.01934868012839793</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.01602824859080769</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.00683128260970459</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.01199529214292365</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3706</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4940</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.005852973394160464</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.001782712148671401</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.005832101557478024</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1353; 7483</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>322; 3659</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2402; 9975</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.03235952089390536</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.02026274193101572</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.02422103137528378</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.07014641825303601</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.03711804879363367</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.05422199189834331</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>11681</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5755</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>17436</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.0401064117138191</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.016628071931758</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.03453662078871862</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>6679; 18886</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2578; 10840</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11106; 26723</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1134127988638529</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.06991722147075764</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.08310365182806735</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.03816867457674666</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.05796291050795187</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.04800026097375424</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>6342</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>9505</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>15847</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.01514687899589644</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.02953215941594477</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.03083385825091068</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>2517; 13781</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>4843; 15888</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>10180; 24882</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.08293302801315364</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.09688878985733924</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.07536583823219772</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.03257159219190062</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.02790148722013043</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.03035931220745052</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>22371</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>17249</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>39620</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.02095011880756617</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.0181705949898663</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.02256034144847768</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>14389; 31658</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>11233; 25225</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>29442; 52502</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.04609328257751053</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.04080404033416259</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.04023056483244414</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen una baja adherencia a la dieta mediterránea (tasa de respuesta: 96,61%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>641</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>756</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>3416</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>3828</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>4673</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>3706</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>4940</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1353</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>322</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>7483</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>3659</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>9975</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>11681</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>5755</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>17436</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>6679</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>2578</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>11106</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>18886</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>10840</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>26723</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>6342</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>9505</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>15847</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>2517</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>4843</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>10180</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>13781</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>15888</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>24882</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>22371</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>17249</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>39620</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>14389</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>11233</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>29442</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>31658</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>25225</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>52502</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>